--- a/research/traditional_assets/database/data/israel/israel_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0558</v>
+        <v>0.11</v>
       </c>
       <c r="E2">
-        <v>0.23</v>
+        <v>0.601</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>28.5</v>
+        <v>34</v>
       </c>
       <c r="L2">
-        <v>0.1505546751188589</v>
+        <v>0.1649684619116934</v>
       </c>
       <c r="M2">
-        <v>1.8645</v>
+        <v>3.09</v>
       </c>
       <c r="N2">
-        <v>0.01229881266490765</v>
+        <v>0.02382420971472629</v>
       </c>
       <c r="O2">
-        <v>0.06542105263157896</v>
+        <v>0.09088235294117647</v>
       </c>
       <c r="P2">
-        <v>1.8645</v>
+        <v>3.09</v>
       </c>
       <c r="Q2">
-        <v>0.01229881266490765</v>
+        <v>0.02382420971472629</v>
       </c>
       <c r="R2">
-        <v>0.06542105263157896</v>
+        <v>0.09088235294117647</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>861.8</v>
+        <v>836.9</v>
       </c>
       <c r="V2">
-        <v>5.684696569920844</v>
+        <v>6.452582883577487</v>
       </c>
       <c r="W2">
-        <v>0.15</v>
+        <v>0.1472498917280208</v>
       </c>
       <c r="X2">
-        <v>0.1635199415885405</v>
+        <v>0.1914619642066382</v>
       </c>
       <c r="Y2">
-        <v>-0.01351994158854047</v>
+        <v>-0.04421207247861744</v>
       </c>
       <c r="Z2">
-        <v>-1.296575342465754</v>
+        <v>1.964728312678742</v>
       </c>
       <c r="AA2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04666327042209671</v>
+        <v>0.06315372002672055</v>
       </c>
       <c r="AC2">
-        <v>-0.04666327042209671</v>
+        <v>-0.06315372002672055</v>
       </c>
       <c r="AD2">
-        <v>735.8</v>
+        <v>828.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>735.8</v>
+        <v>828.4</v>
       </c>
       <c r="AG2">
-        <v>-126</v>
+        <v>-8.5</v>
       </c>
       <c r="AH2">
-        <v>0.8291638494478251</v>
+        <v>0.8646279094040289</v>
       </c>
       <c r="AI2">
-        <v>0.7250689791091841</v>
+        <v>0.7342018966586901</v>
       </c>
       <c r="AJ2">
-        <v>-4.921875000000001</v>
+        <v>-0.07013201320132013</v>
       </c>
       <c r="AK2">
-        <v>-0.8235294117647058</v>
+        <v>-0.02916952642415923</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0558</v>
+        <v>0.11</v>
       </c>
       <c r="E3">
-        <v>0.23</v>
+        <v>0.601</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>28.5</v>
+        <v>34</v>
       </c>
       <c r="L3">
-        <v>0.1505546751188589</v>
+        <v>0.1649684619116934</v>
       </c>
       <c r="M3">
-        <v>1.8645</v>
+        <v>3.09</v>
       </c>
       <c r="N3">
-        <v>0.01229881266490765</v>
+        <v>0.02382420971472629</v>
       </c>
       <c r="O3">
-        <v>0.06542105263157896</v>
+        <v>0.09088235294117647</v>
       </c>
       <c r="P3">
-        <v>1.8645</v>
+        <v>3.09</v>
       </c>
       <c r="Q3">
-        <v>0.01229881266490765</v>
+        <v>0.02382420971472629</v>
       </c>
       <c r="R3">
-        <v>0.06542105263157896</v>
+        <v>0.09088235294117647</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>861.8</v>
+        <v>836.9</v>
       </c>
       <c r="V3">
-        <v>5.684696569920844</v>
+        <v>6.452582883577487</v>
       </c>
       <c r="W3">
-        <v>0.15</v>
+        <v>0.1472498917280208</v>
       </c>
       <c r="X3">
-        <v>0.1635199415885405</v>
+        <v>0.1914619642066382</v>
       </c>
       <c r="Y3">
-        <v>-0.01351994158854047</v>
+        <v>-0.04421207247861744</v>
       </c>
       <c r="Z3">
-        <v>-1.296575342465754</v>
+        <v>1.964728312678742</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04666327042209671</v>
+        <v>0.06315372002672055</v>
       </c>
       <c r="AC3">
-        <v>-0.04666327042209671</v>
+        <v>-0.06315372002672055</v>
       </c>
       <c r="AD3">
-        <v>735.8</v>
+        <v>828.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>735.8</v>
+        <v>828.4</v>
       </c>
       <c r="AG3">
-        <v>-126</v>
+        <v>-8.5</v>
       </c>
       <c r="AH3">
-        <v>0.8291638494478251</v>
+        <v>0.8646279094040289</v>
       </c>
       <c r="AI3">
-        <v>0.7250689791091841</v>
+        <v>0.7342018966586901</v>
       </c>
       <c r="AJ3">
-        <v>-4.921875000000001</v>
+        <v>-0.07013201320132013</v>
       </c>
       <c r="AK3">
-        <v>-0.8235294117647058</v>
+        <v>-0.02916952642415923</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/israel/israel_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.11</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="E2">
-        <v>0.601</v>
+        <v>0.174</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L2">
-        <v>0.1649684619116934</v>
+        <v>0.1564027370478983</v>
       </c>
       <c r="M2">
-        <v>3.09</v>
+        <v>5.96</v>
       </c>
       <c r="N2">
-        <v>0.02382420971472629</v>
+        <v>0.04591679506933743</v>
       </c>
       <c r="O2">
-        <v>0.09088235294117647</v>
+        <v>0.18625</v>
       </c>
       <c r="P2">
-        <v>3.09</v>
+        <v>5.96</v>
       </c>
       <c r="Q2">
-        <v>0.02382420971472629</v>
+        <v>0.04591679506933743</v>
       </c>
       <c r="R2">
-        <v>0.09088235294117647</v>
+        <v>0.18625</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>836.9</v>
+        <v>900.5</v>
       </c>
       <c r="V2">
-        <v>6.452582883577487</v>
+        <v>6.937596302003081</v>
       </c>
       <c r="W2">
-        <v>0.1472498917280208</v>
+        <v>0.1318500206015657</v>
       </c>
       <c r="X2">
-        <v>0.1914619642066382</v>
+        <v>0.1422617672340771</v>
       </c>
       <c r="Y2">
-        <v>-0.04421207247861744</v>
+        <v>-0.01041174663251135</v>
       </c>
       <c r="Z2">
-        <v>1.964728312678742</v>
+        <v>0.873612297181896</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06315372002672055</v>
+        <v>0.05354350269423599</v>
       </c>
       <c r="AC2">
-        <v>-0.06315372002672055</v>
+        <v>-0.05354350269423599</v>
       </c>
       <c r="AD2">
-        <v>828.4</v>
+        <v>889.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>828.4</v>
+        <v>889.6</v>
       </c>
       <c r="AG2">
-        <v>-8.5</v>
+        <v>-10.89999999999998</v>
       </c>
       <c r="AH2">
-        <v>0.8646279094040289</v>
+        <v>0.8726701981557778</v>
       </c>
       <c r="AI2">
-        <v>0.7342018966586901</v>
+        <v>0.7399151626050071</v>
       </c>
       <c r="AJ2">
-        <v>-0.07013201320132013</v>
+        <v>-0.09167367535744302</v>
       </c>
       <c r="AK2">
-        <v>-0.02916952642415923</v>
+        <v>-0.03611663353214041</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.11</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="E3">
-        <v>0.601</v>
+        <v>0.174</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L3">
-        <v>0.1649684619116934</v>
+        <v>0.1564027370478983</v>
       </c>
       <c r="M3">
-        <v>3.09</v>
+        <v>5.96</v>
       </c>
       <c r="N3">
-        <v>0.02382420971472629</v>
+        <v>0.04591679506933743</v>
       </c>
       <c r="O3">
-        <v>0.09088235294117647</v>
+        <v>0.18625</v>
       </c>
       <c r="P3">
-        <v>3.09</v>
+        <v>5.96</v>
       </c>
       <c r="Q3">
-        <v>0.02382420971472629</v>
+        <v>0.04591679506933743</v>
       </c>
       <c r="R3">
-        <v>0.09088235294117647</v>
+        <v>0.18625</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>836.9</v>
+        <v>900.5</v>
       </c>
       <c r="V3">
-        <v>6.452582883577487</v>
+        <v>6.937596302003081</v>
       </c>
       <c r="W3">
-        <v>0.1472498917280208</v>
+        <v>0.1318500206015657</v>
       </c>
       <c r="X3">
-        <v>0.1914619642066382</v>
+        <v>0.1422617672340771</v>
       </c>
       <c r="Y3">
-        <v>-0.04421207247861744</v>
+        <v>-0.01041174663251135</v>
       </c>
       <c r="Z3">
-        <v>1.964728312678742</v>
+        <v>0.873612297181896</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06315372002672055</v>
+        <v>0.05354350269423599</v>
       </c>
       <c r="AC3">
-        <v>-0.06315372002672055</v>
+        <v>-0.05354350269423599</v>
       </c>
       <c r="AD3">
-        <v>828.4</v>
+        <v>889.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>828.4</v>
+        <v>889.6</v>
       </c>
       <c r="AG3">
-        <v>-8.5</v>
+        <v>-10.89999999999998</v>
       </c>
       <c r="AH3">
-        <v>0.8646279094040289</v>
+        <v>0.8726701981557778</v>
       </c>
       <c r="AI3">
-        <v>0.7342018966586901</v>
+        <v>0.7399151626050071</v>
       </c>
       <c r="AJ3">
-        <v>-0.07013201320132013</v>
+        <v>-0.09167367535744302</v>
       </c>
       <c r="AK3">
-        <v>-0.02916952642415923</v>
+        <v>-0.03611663353214041</v>
       </c>
       <c r="AL3">
         <v>0</v>
